--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486901_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486901_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4081</v>
+        <v>10.5842</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5511</v>
+        <v>10.3419</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.143</v>
+        <v>0.2423</v>
       </c>
       <c r="G2" t="n">
         <v>8.327299999999999</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7953</v>
+        <v>0.9714</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2434</v>
+        <v>1.0342</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4482</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1786</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.03</v>
+        <v>5.4651</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5768</v>
+        <v>3.3676</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4532</v>
+        <v>2.0975</v>
       </c>
       <c r="G3" t="n">
         <v>4.9967</v>
@@ -688,13 +688,13 @@
         <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9984</v>
+        <v>1.4335</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1544</v>
+        <v>0.9452</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8441</v>
+        <v>0.4883</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3491</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3478</v>
+        <v>5.3321</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6468</v>
+        <v>6.5422</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.299</v>
+        <v>-1.2101</v>
       </c>
       <c r="G4" t="n">
         <v>4.2421</v>
@@ -766,13 +766,13 @@
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5513</v>
+        <v>0.5356</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6042</v>
+        <v>0.4996</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0529</v>
+        <v>0.036</v>
       </c>
       <c r="V4" t="n">
         <v>0.3491</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8019</v>
+        <v>3.5787</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1391</v>
+        <v>1.0345</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6628</v>
+        <v>2.5442</v>
       </c>
       <c r="G5" t="n">
         <v>4.5047</v>
@@ -844,13 +844,13 @@
         <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9399</v>
+        <v>0.7168</v>
       </c>
       <c r="T5" t="n">
-        <v>0.244</v>
+        <v>0.1394</v>
       </c>
       <c r="U5" t="n">
-        <v>0.696</v>
+        <v>0.5774</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4481</v>
+        <v>1.4341</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6926</v>
+        <v>2.7972</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2445</v>
+        <v>-1.3631</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6777</v>
@@ -922,13 +922,13 @@
         <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9554</v>
+        <v>0.9414</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9568</v>
+        <v>1.0614</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0014</v>
+        <v>-0.12</v>
       </c>
       <c r="V6" t="n">
         <v>0.3491</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. TERREROS RIVAS</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.1132</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0313</v>
+        <v>-1.5114</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9641</v>
+        <v>1.6246</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3957</v>
+        <v>-2.5339</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0907</v>
+        <v>-1.0445</v>
       </c>
       <c r="I7" t="n">
-        <v>0.305</v>
+        <v>-1.4893</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2135</v>
+        <v>-2.8372</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7008</v>
+        <v>-1.0214</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5127</v>
+        <v>-1.8158</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8177</v>
+        <v>0.3034</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6101</v>
+        <v>-0.0231</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2077</v>
+        <v>0.3264</v>
       </c>
       <c r="P7" t="n">
         <v>0.616</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4743</v>
+        <v>0.6122</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0232</v>
+        <v>0.4532</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4511</v>
+        <v>0.159</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4189</v>
+        <v>1.4189</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.8993</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4189</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. CARREIRA KREPS</t>
+          <t>I. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0979</v>
+        <v>0.0985</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4397</v>
+        <v>1.2405</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5376</v>
+        <v>-1.142</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0672</v>
+        <v>0.3957</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1459</v>
+        <v>0.0907</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.213</v>
+        <v>0.305</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8586</v>
+        <v>1.2135</v>
       </c>
       <c r="K8" t="n">
         <v>0.7008</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1579</v>
+        <v>0.5127</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9258</v>
+        <v>-0.8177</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.6101</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3709</v>
+        <v>-0.2077</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3614</v>
+        <v>0.5056</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.2324</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2197</v>
+        <v>0.2732</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4189</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>M. CARREIRA KREPS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2146</v>
+        <v>-0.1136</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7206</v>
+        <v>1.3351</v>
       </c>
       <c r="F9" t="n">
-        <v>1.506</v>
+        <v>-1.4487</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5339</v>
+        <v>-0.0672</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0445</v>
+        <v>0.1459</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4893</v>
+        <v>-0.213</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.8372</v>
+        <v>0.8586</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0214</v>
+        <v>0.7008</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8158</v>
+        <v>0.1579</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3034</v>
+        <v>-0.9258</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0231</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3264</v>
+        <v>-0.3709</v>
       </c>
       <c r="P9" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2844</v>
+        <v>0.3457</v>
       </c>
       <c r="T9" t="n">
-        <v>0.244</v>
+        <v>0.4765</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0404</v>
+        <v>-0.1307</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4189</v>
+        <v>-1.4189</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8993</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4805</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3642</v>
+        <v>-1.3206</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8176</v>
+        <v>1.713</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1819</v>
+        <v>-3.0336</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1432</v>
@@ -1234,13 +1234,13 @@
         <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0828</v>
+        <v>1.1264</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9568</v>
+        <v>0.8522</v>
       </c>
       <c r="U10" t="n">
-        <v>0.126</v>
+        <v>0.2743</v>
       </c>
       <c r="V10" t="n">
         <v>-3.5359</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.255</v>
+        <v>-4.0005</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6097</v>
+        <v>-3.2959</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6453</v>
+        <v>-0.7046</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9171</v>
@@ -1312,13 +1312,13 @@
         <v>1.6427</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5184</v>
+        <v>0.7729</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3253</v>
+        <v>0.6391</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1931</v>
+        <v>0.1338</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>21.1713</v>
+        <v>21.1712</v>
       </c>
       <c r="E12" t="n">
         <v>23.5647</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3934</v>
+        <v>-2.3935</v>
       </c>
       <c r="G12" t="n">
         <v>15.1274</v>
@@ -1390,7 +1390,7 @@
         <v>16.4273</v>
       </c>
       <c r="S12" t="n">
-        <v>7.9616</v>
+        <v>7.961500000000001</v>
       </c>
       <c r="T12" t="n">
         <v>6.333200000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.162</v>
+        <v>3.5325</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6549</v>
+        <v>5.1319</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.493</v>
+        <v>-1.5994</v>
       </c>
       <c r="G13" t="n">
         <v>2.6753</v>
@@ -1468,13 +1468,13 @@
         <v>1.2321</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2546</v>
+        <v>-0.3748</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6778</v>
+        <v>0.1548</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4232</v>
+        <v>-0.5296</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2656</v>
+        <v>0.5512</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7481</v>
+        <v>2.3354</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4825</v>
+        <v>-1.7842</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.1823</v>
+        <v>-1.0259</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.1248</v>
+        <v>0.2761</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0575</v>
+        <v>-1.302</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.907</v>
+        <v>1.8879</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9859</v>
+        <v>1.9408</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0789</v>
+        <v>-0.0529</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2753</v>
+        <v>-2.9138</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1389</v>
+        <v>-1.6646</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1365</v>
+        <v>-1.2491</v>
       </c>
       <c r="P14" t="n">
-        <v>1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2321</v>
+        <v>2.0534</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0988</v>
+        <v>-1.0635</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2362</v>
+        <v>-0.1397</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1374</v>
+        <v>-0.9238</v>
       </c>
       <c r="V14" t="n">
-        <v>2.117</v>
+        <v>3.6673</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4189</v>
+        <v>3.6673</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ARRIBAS GOMEZ</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4567</v>
+        <v>0.1549</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0464</v>
+        <v>3.5944</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4103</v>
+        <v>-3.4396</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2909</v>
+        <v>-2.151</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0357</v>
+        <v>-2.5434</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2552</v>
+        <v>0.3923</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0195</v>
+        <v>1.5628</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0195</v>
+        <v>-0.2657</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.8285</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3104</v>
+        <v>-3.7138</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0552</v>
+        <v>-2.2777</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2552</v>
+        <v>-1.4361</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1658</v>
+        <v>-1.2834</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0659</v>
+        <v>-0.3256</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0999</v>
+        <v>-0.9578</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.61</v>
+        <v>0.0476</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1262</v>
+        <v>0.5389</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7362</v>
+        <v>-0.4913</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0259</v>
+        <v>-3.1823</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2761</v>
+        <v>-2.1248</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.302</v>
+        <v>-1.0575</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8879</v>
+        <v>-0.907</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9408</v>
+        <v>-0.9859</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0529</v>
+        <v>0.0789</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.9138</v>
+        <v>-2.2753</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6646</v>
+        <v>-1.1389</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2491</v>
+        <v>-1.1365</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0534</v>
+        <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.2247</v>
+        <v>-0.1191</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3489</v>
+        <v>0.027</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.8758</v>
+        <v>-0.1462</v>
       </c>
       <c r="V16" t="n">
-        <v>3.6673</v>
+        <v>2.117</v>
       </c>
       <c r="W16" t="n">
-        <v>3.6673</v>
+        <v>1.4189</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>P. ARRIBAS GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7953</v>
+        <v>-0.1534</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0714</v>
+        <v>0.0582</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.8667</v>
+        <v>-0.2116</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.151</v>
+        <v>-0.2909</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.5434</v>
+        <v>-0.0357</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3923</v>
+        <v>-0.2552</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5628</v>
+        <v>0.0195</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2657</v>
+        <v>0.0195</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8285</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.7138</v>
+        <v>-0.3104</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.2777</v>
+        <v>-0.0552</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4361</v>
+        <v>-0.2552</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.2336</v>
+        <v>0.1375</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8486</v>
+        <v>0.0387</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.3849</v>
+        <v>0.0988</v>
       </c>
       <c r="V17" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9819</v>
+        <v>-1.8482</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1494</v>
+        <v>0.7214</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8325</v>
+        <v>-2.5696</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2988</v>
+        <v>-0.1853</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.531</v>
+        <v>0.9117</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7679</v>
+        <v>-1.097</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0708</v>
+        <v>1.7559</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0871</v>
+        <v>1.7164</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1579</v>
+        <v>0.0395</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3696</v>
+        <v>-1.9412</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4439</v>
+        <v>-0.8047</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9257</v>
+        <v>-1.1365</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.4374</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5757</v>
+        <v>-0.0736</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4411</v>
+        <v>-0.248</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1347</v>
+        <v>0.1744</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1786</v>
+        <v>-1.1786</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4189</v>
+        <v>0.2402</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2402</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4716</v>
+        <v>-1.884</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1398</v>
+        <v>-0.4368</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6114</v>
+        <v>-1.4472</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1853</v>
+        <v>-1.1533</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9117</v>
+        <v>0.428</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.097</v>
+        <v>-1.5813</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7559</v>
+        <v>0.23</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7164</v>
+        <v>0.9538</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0395</v>
+        <v>-0.7238</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9412</v>
+        <v>-1.3833</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8047</v>
+        <v>-0.5258</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1365</v>
+        <v>-0.8575</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>0.303</v>
+        <v>-0.587</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1704</v>
+        <v>-0.3178</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1326</v>
+        <v>-0.2692</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1786</v>
+        <v>-0.3491</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2402</v>
+        <v>-0.3491</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5709</v>
+        <v>-2.3087</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.646</v>
+        <v>-1.0908</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9248</v>
+        <v>-1.2178</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1533</v>
+        <v>-2.2988</v>
       </c>
       <c r="H20" t="n">
-        <v>0.428</v>
+        <v>-1.531</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5813</v>
+        <v>-0.7679</v>
       </c>
       <c r="J20" t="n">
-        <v>0.23</v>
+        <v>0.0708</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9538</v>
+        <v>-0.0871</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7238</v>
+        <v>0.1579</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3833</v>
+        <v>-2.3696</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5258</v>
+        <v>-1.4439</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8575</v>
+        <v>-0.9257</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2053</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2739</v>
+        <v>0.249</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.527</v>
+        <v>0.4996</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7469</v>
+        <v>-0.2507</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3491</v>
+        <v>1.1786</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3491</v>
+        <v>1.4189</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6103</v>
+        <v>-3.4395</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6151</v>
+        <v>-1.4059</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9951</v>
+        <v>-2.0335</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2709</v>
@@ -2092,13 +2092,13 @@
         <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3394</v>
+        <v>-0.1685</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4611</v>
+        <v>-0.2519</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1217</v>
+        <v>0.0834</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1786</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6293</v>
+        <v>-3.843</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0524</v>
+        <v>-0.634</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5769</v>
+        <v>-3.209</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1165</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2541</v>
+        <v>-0.4678</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8563</v>
+        <v>-0.4379</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3978</v>
+        <v>-0.0299</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5893</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.4729</v>
+        <v>-9.1914</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.8376</v>
+        <v>-6.4192</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6352</v>
+        <v>-2.7722</v>
       </c>
       <c r="G23" t="n">
         <v>-6.1277</v>
@@ -2248,13 +2248,13 @@
         <v>1.4374</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.7024</v>
+        <v>-1.4209</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0462</v>
+        <v>-0.6278</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.6562</v>
+        <v>-0.7931</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-21.1713</v>
+        <v>-18.382</v>
       </c>
       <c r="E24" t="n">
-        <v>2.393499999999998</v>
+        <v>2.3935</v>
       </c>
       <c r="F24" t="n">
-        <v>-23.5646</v>
+        <v>-20.7754</v>
       </c>
       <c r="G24" t="n">
         <v>-15.1273</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.8548</v>
+        <v>-5.854800000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-9.2727</v>
@@ -2326,13 +2326,13 @@
         <v>12.3206</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.9618</v>
+        <v>-5.172099999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.6285</v>
+        <v>-1.6286</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.333100000000001</v>
+        <v>-3.5437</v>
       </c>
       <c r="V24" t="n">
         <v>6.0246</v>
